--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT PreNUDGE ISCED 2011 Education Level Codes</t>
+    <t>AT PreNUDGE ISCED-based Education Category Codes</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Local representation of ISCED 2011 education levels for the highest completed education level used in PreNUDGE. Austrian levels are described at https://bildungssystem.oead.at/isced-klassifikation</t>
+    <t>Local representation of the eight ISCED-based answer categories for the highest completed education level used in PreNUDGE.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>11</t>
+    <t>10</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,58 +144,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>isced-0</t>
-  </si>
-  <si>
-    <t>ISCED 0 - Elementarbereich</t>
-  </si>
-  <si>
     <t>isced-1</t>
   </si>
   <si>
-    <t>ISCED 1 - Primarbereich</t>
+    <t>ISCED 1: Volksschule</t>
   </si>
   <si>
     <t>isced-2</t>
   </si>
   <si>
-    <t>ISCED 2 - Sekundarbereich I</t>
-  </si>
-  <si>
-    <t>isced-3</t>
-  </si>
-  <si>
-    <t>ISCED 3 - Sekundarbereich II</t>
+    <t>ISCED 2: Hauptschule, Mittelschulen, Unterstufen von AHS</t>
+  </si>
+  <si>
+    <t>isced-3a</t>
+  </si>
+  <si>
+    <t>ISCED 3a: Polytechnische Schule</t>
+  </si>
+  <si>
+    <t>isced-3b</t>
+  </si>
+  <si>
+    <t>ISCED 3b: Berufsbildende mittlere Schulen (HASCH, Fachschulen)</t>
+  </si>
+  <si>
+    <t>isced-3c</t>
+  </si>
+  <si>
+    <t>ISCED 3c: Berufsbildende höhere Schulen (HAK, HBLA, HTL) und AHS-Oberstufe</t>
   </si>
   <si>
     <t>isced-4</t>
   </si>
   <si>
-    <t>ISCED 4 - Postsekundarer, nicht tertiärer Bereich</t>
+    <t>ISCED 4: Lehre mit Matura, Gesundheits- und Krankenpflegeschule (nicht-tertiär), Meister- oder Diplomprüfung</t>
   </si>
   <si>
     <t>isced-5</t>
   </si>
   <si>
-    <t>ISCED 5 - Kurzes tertiäres Bildungsprogramm</t>
-  </si>
-  <si>
-    <t>isced-6</t>
-  </si>
-  <si>
-    <t>ISCED 6 - Bachelor- bzw. gleichwertiges Bildungsprogramm</t>
-  </si>
-  <si>
-    <t>isced-7</t>
-  </si>
-  <si>
-    <t>ISCED 7 - Master- bzw. gleichwertiges Bildungsprogramm</t>
-  </si>
-  <si>
-    <t>isced-8</t>
-  </si>
-  <si>
-    <t>ISCED 8 - Promotion bzw. gleichwertiges Bildungsprogramm</t>
+    <t>ISCED 5: Kolleg, tertiäre Hebammenakademien bzw. medizinisch-technische Ausbildungen im Kurzzyklus</t>
+  </si>
+  <si>
+    <t>isced-6-8</t>
+  </si>
+  <si>
+    <t>ISCED 6–8: Hochschulabschlüsse (Bachelor, Master, Doktor)</t>
   </si>
   <si>
     <t>unknown</t>
@@ -525,7 +519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -662,18 +656,6 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>8</t>
   </si>
   <si>
     <t>Level</t>
@@ -190,18 +190,6 @@
   </si>
   <si>
     <t>ISCED 6–8: Hochschulabschlüsse (Bachelor, Master, Doktor)</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>Weiß nicht</t>
-  </si>
-  <si>
-    <t>not-stated</t>
-  </si>
-  <si>
-    <t>Keine Angabe</t>
   </si>
 </sst>
 </file>
@@ -519,7 +507,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -632,30 +620,6 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-prenudge-isced-2011-education-level.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
